--- a/SocialPerks_Restaurants_Paris_New.xlsx
+++ b/SocialPerks_Restaurants_Paris_New.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Nouveaux Restaurants Paris" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Paris New Leads - SocialPerks" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,11 +71,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -120,12 +115,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -500,7 +489,7 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -525,7 +514,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Arr.</t>
+          <t>Arrondissement</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -580,42 +569,42 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Café Lomi</t>
+          <t>Septime</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>18e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>3bis rue Marcadet, 75018 Paris</t>
+          <t>80 rue de Charonne, 75011 Paris</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>contact@lomi.paris</t>
+          <t>reservation@septime-charonne.fr</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>+33 9 80 39 56 24</t>
+          <t>+33 1 43 67 38 29</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>lomi.paris</t>
+          <t>septime-charonne.fr</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>@lomi.paris</t>
+          <t>@septime_paris</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Specialty Coffee / Torréfaction</t>
+          <t>Bistronomie / Farm-to-table</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -630,7 +619,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>Torréfacteur indépendant du 18e, brunch photogénique et café de qualité</t>
+          <t>Uno dei bistrot più acclamati di Parigi, presentazioni minimaliste molto fotografate</t>
         </is>
       </c>
     </row>
@@ -640,42 +629,38 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Télescope</t>
+          <t>Clown Bar</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>1er</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>5 rue Villedo, 75001 Paris</t>
+          <t>114 rue Amelot, 75011 Paris</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>contact@telescopecafe.com</t>
+          <t>clownbar.paris@gmail.com</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 61 33 14</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>telescopecafe.com</t>
-        </is>
-      </c>
+          <t>+33 1 43 55 87 35</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>@telescopecafe</t>
+          <t>@clownbarofficial</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Specialty Coffee</t>
+          <t>Natural Wine / Bistro / Art</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -690,7 +675,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Pionnière du café de spécialité à Paris, minimaliste et instagrammable</t>
+          <t>Ex-bar del circo con affreschi Art Nouveau, uno dei più instagrammabili di Parigi</t>
         </is>
       </c>
     </row>
@@ -700,42 +685,42 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ten Belles</t>
+          <t>Le Mary Celeste</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10e</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>10 rue de la Grange aux Belles, 75010 Paris</t>
+          <t>1 rue Commines, 75003 Paris</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>contact@tenbelles.com</t>
+          <t>contact@lemaryceleste.com</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 40 90 78</t>
+          <t>+33 1 42 77 23 32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>tenbelles.com</t>
+          <t>lemaryceleste.com</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>@tenbelles</t>
+          <t>@lemaryceleste</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Specialty Coffee / Brunch</t>
+          <t>Oyster Bar / Cocktails</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -750,47 +735,55 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Café de spécialité iconique du canal Saint-Martin, brunch et gâteaux</t>
+          <t>Ostricheria-cocktail bar nel Marais, ostriche e drinks fotogenici</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Boot Café</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>3e</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>19 rue du Pont aux Choux, 75003 Paris</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>+33 6 78 81 97 00</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>@bootcafe</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Specialty Coffee</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Frenchie</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2e</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>5 rue du Nil, 75002 Paris</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>contact@frenchie-restaurant.com</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 40 39 96 19</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>frenchie-restaurant.com</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>@frenchierestaurant</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Bistronomie Moderne</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Indipendente</t>
         </is>
@@ -800,9 +793,9 @@
           <t>✅ Sì</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Minuscolo caffè in una ex-calzoleria, uno dei più instagrammabili di Parigi</t>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Bistrot gastronomique iconico del 2e, sala piccola e molto prenotata</t>
         </is>
       </c>
     </row>
@@ -812,47 +805,47 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Café Oberkampf</t>
+          <t>Café Kitsuné</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>1er / Palais-Royal</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3 rue Neuve Popincourt, 75011 Paris</t>
+          <t>51 galerie de Montpensier, 75001 Paris</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>contact@cafeoberkampf.com</t>
+          <t>contact@cafekitsune.com</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 57 28 55</t>
+          <t>+33 1 42 60 97 53</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>cafeoberkampf.com</t>
+          <t>cafekitsune.com</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>@cafeoberkampf</t>
+          <t>@cafekitsune</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Café / Brunch</t>
+          <t>Specialty Coffee / Japonais</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Indipendente</t>
+          <t>Piccola catena</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -862,7 +855,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Brunch colorato nel quartiere Oberkampf, interni curati e photogéniques</t>
+          <t>Caffè fashion-forward nei giardini del Palais-Royal, colazioni iconiche</t>
         </is>
       </c>
     </row>
@@ -872,57 +865,57 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Café Kitsuné</t>
+          <t>Broken Arm</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1er/6e/8e</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>51 Galerie de Montpensier, 75001 Paris</t>
+          <t>12 rue Perrée, 75003 Paris</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>cafe@maisonkitsune.com</t>
+          <t>contact@the-broken-arm.com</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>+33 1 40 15 62 32</t>
+          <t>+33 1 44 61 53 60</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>maisonkitsune.com</t>
+          <t>the-broken-arm.com</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>@cafekitsune</t>
+          <t>@thebrokenarm</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Japanese Café / Design</t>
+          <t>Café / Concept Store / Design</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Caffè fashion e musica, interni epurati e molto fotografabili</t>
+          <t>Caffè nel concept store design del Marais, interni minimal très fotografati</t>
         </is>
       </c>
     </row>
@@ -932,47 +925,47 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fragments</t>
+          <t>Ten Belles</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>10e / Canal Saint-Martin</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>76 rue des Tournelles, 75003 Paris</t>
+          <t>10 rue de la Grange aux Belles, 75010 Paris</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>contact@fragmentscafe.com</t>
+          <t>hello@tenbelles.com</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>+33 9 67 97 87 48</t>
+          <t>+33 1 42 40 90 78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>fragmentscafe.com</t>
+          <t>tenbelles.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>@fragmentsparis</t>
+          <t>@tenbelles</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Specialty Coffee / Natural Wine</t>
+          <t>Specialty Coffee / Brunch</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Indipendente</t>
+          <t>Piccola catena</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -982,7 +975,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Caffè e vini naturali nel Marais, atmosfera curata e bohémien</t>
+          <t>Specialty coffee sul Canal Saint-Martin, brunch e latte art fotogenici</t>
         </is>
       </c>
     </row>
@@ -992,42 +985,42 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>KB CaféShop</t>
+          <t>Le Servan</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>53 ave Trudaine, 75009 Paris</t>
+          <t>32 rue Saint-Maur, 75011 Paris</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>contact@kbcafeshop.com</t>
+          <t>leservan@gmail.com</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>+33 1 56 92 12 41</t>
+          <t>+33 1 55 28 51 82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>kbcafeshop.com</t>
+          <t>leservan.com</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>@kbcafeshop</t>
+          <t>@leservan_paris</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Specialty Coffee / Brunch</t>
+          <t>Bistronomie Franco-Asiatique</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1042,7 +1035,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Caffè australiano nel 9e, brunch copioso e molto fotografabile</t>
+          <t>Bistrot franco-asiatico dell'11e, piatti fusion creativi fotografabili</t>
         </is>
       </c>
     </row>
@@ -1052,47 +1045,43 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Café Pinson</t>
+          <t>Yard Wine Bar</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3e/10e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6 rue du Forez, 75003 Paris</t>
+          <t>6 rue de Mont-Louis, 75011 Paris</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>contact@cafepinson.fr</t>
+          <t>yard.paris@gmail.com</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>+33 9 83 82 53 60</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>cafepinson.fr</t>
-        </is>
-      </c>
+          <t>+33 1 40 09 70 30</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>@cafepinson</t>
+          <t>@yardwinebar</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Café / Healthy / Végane</t>
+          <t>Natural Wine Bar / Courtyard</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
+          <t>Indipendente</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1102,7 +1091,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>Café végane et biologique, plats colorés et instagrammables</t>
+          <t>Wine bar con courtyard interieur, vini naturali e atmosfera cave fotogenica</t>
         </is>
       </c>
     </row>
@@ -1112,42 +1101,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Café Méricourt</t>
+          <t>Le Grand Bain</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>20e / Belleville</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>22 rue de la Folie-Méricourt, 75011 Paris</t>
+          <t>14 rue Denoyez, 75020 Paris</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>contact@cafemericourt.com</t>
+          <t>contact@legrandbain.fr</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 38 94 04</t>
+          <t>+33 1 58 30 88 07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>cafemericourt.com</t>
+          <t>legrandbain.fr</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>@cafemericourt</t>
+          <t>@legrandbain</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Café / Brunch</t>
+          <t>Natural Wine / Bistronomie</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1162,7 +1151,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Brunch du weekend iconique dans le 11e, oeuf bénédictine photogénique</t>
+          <t>Bistrot e wine bar nel cuore di Belleville, street art e atmosfera fotografabile</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1161,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Yard</t>
+          <t>Café Oberkampf</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1182,32 +1171,28 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6 rue Mont Louis, 75011 Paris</t>
+          <t>3 rue Neuve Popincourt, 75011 Paris</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>contact@yardparis.com</t>
+          <t>cafeoberkampf@gmail.com</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>+33 1 40 09 70 30</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>yardparis.com</t>
-        </is>
-      </c>
+          <t>+33 1 43 57 75 47</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>@yard.paris</t>
+          <t>@cafeoberkampf</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Wine Bar / Bistro</t>
+          <t>Café / Brunch / Bar</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1222,7 +1207,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Cave à manger naturel dans le 11e, planches photogéniques</t>
+          <t>Caffè e brunch all'Oberkampf, atmosfera hipster e terrasse fotografabile</t>
         </is>
       </c>
     </row>
@@ -1232,42 +1217,42 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Clown Bar</t>
+          <t>Buvette Gastrothèque</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>9e / Pigalle</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>114 rue Amelot, 75011 Paris</t>
+          <t>28 rue Henry Monnier, 75009 Paris</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>contact@clown-bar-paris.fr</t>
+          <t>contact@ilovebuvette.com</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 55 87 35</t>
+          <t>+33 1 44 63 41 71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>clown-bar-paris.fr</t>
+          <t>ilovebuvette.com</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>@clownbarparis</t>
+          <t>@ilovebuvette</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Bistro / Natural Wine</t>
+          <t>French / Wine / Cosy</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1275,14 +1260,14 @@
           <t>Indipendente</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Bar à vins naturels dans l'ancien décor du Cirque d'Hiver, unique</t>
+          <t>Gastrothèque dal decor vintage nel SoPi, ardoise e bottiglie fotogenici</t>
         </is>
       </c>
     </row>
@@ -1292,42 +1277,42 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Mokonuts</t>
+          <t>Holybelly 5</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>10e / Canal</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5 rue Saint-Bernard, 75011 Paris</t>
+          <t>5 rue Lucien Sampaix, 75010 Paris</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>mokonuts@mokonuts.com</t>
+          <t>contact@holybelly.fr</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>+33 9 80 81 82 85</t>
+          <t>+33 1 82 28 00 80</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>mokonuts.com</t>
+          <t>holybelly.fr</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>@mokonuts</t>
+          <t>@holybelly5</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Café / Middle-Eastern / Bakery</t>
+          <t>Brunch / Coffee / Australian</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1342,7 +1327,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Pâtisseries créatives et cuisine Moyen-Orient, cookies instagrammés partout</t>
+          <t>Brunch australiano sul Canal Saint-Martin, pancakes e flat white iconici</t>
         </is>
       </c>
     </row>
@@ -1352,42 +1337,42 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Le Mary Celeste</t>
+          <t>Balagan</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>1er</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1 rue Commines, 75003 Paris</t>
+          <t>9 rue d'Alger, 75001 Paris</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>contact@lemaryceleste.com</t>
+          <t>contact@balagan-paris.com</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>+33 9 80 72 98 83</t>
+          <t>+33 1 40 20 72 14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>lemaryceleste.com</t>
+          <t>balagan-paris.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>@lemaryceleste</t>
+          <t>@balaganparis</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Cocktail Bar / Tapas</t>
+          <t>Israeli / Middle Eastern</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1402,51 +1387,51 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Bar à cocktails et tapas dans le Marais, décor marin très photogénique</t>
+          <t>Cucina israeliana gourmet nel 1er, mezzé colorati e hummus fotografabile</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Septime La Cave</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Perché</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>11e</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>3 rue Basfroi, 75011 Paris</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>+33 1 43 67 14 87</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>septime-lacave.fr</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>@septimeparis</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Cave à Manger / Natural Wine</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>7 rue de la Forge Royale, 75011 Paris</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>perche.paris@gmail.com</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 43 70 26 27</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>@perche_paris</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Café / Brunch / Terrasse</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Indipendente</t>
         </is>
@@ -1456,49 +1441,53 @@
           <t>✅ Sì</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>Cave à vins naturels du célèbre Septime, planches de charcuterie et fromages</t>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Caffè con terrasse segreta nell'11e, piatti colorati e giardino segreto</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Aux Deux Amis</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Le Petit Keller</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>11e</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>45 rue Oberkampf, 75011 Paris</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>+33 1 58 30 38 13</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>@auxdeuxamis11</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Bistro / Tapas / Natural Wine</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>13 rue Keller, 75011 Paris</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>lepetikkeller@gmail.com</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 47 00 12 97</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>@lepetikeller</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Bistro / Natural Wine</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Indipendente</t>
         </is>
@@ -1508,49 +1497,57 @@
           <t>✅ Sì</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>Bar à vins nature avec petits plats, atmosphère conviviale instagrammable</t>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Piccolo bistrot a vini naturali a Bastille, atmosfera intima e fotografabile</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Camille Surnom</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>3e</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>24 rue des Francs Bourgeois, 75003 Paris</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>+33 1 42 72 20 50</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>@camillesurnom</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>Bistro Parisien</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Fulgurances L'Adresse</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>11e</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>10 rue Alexandre Dumas, 75011 Paris</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>contact@fulgurances.com</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 71 19 37 37</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>fulgurances.com</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>@fulgurances</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Pop-up / Chef en Résidence</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Indipendente</t>
         </is>
@@ -1560,9 +1557,9 @@
           <t>✅ Sì</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>Bistrot classique avec terrasse sur le Marais, cuisine simple et belle</t>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Ristorante pop-up con chef en résidence, piatti innovativi molto fotografati</t>
         </is>
       </c>
     </row>
@@ -1572,97 +1569,105 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Breizh Café Marais</t>
+          <t>Mokonuts</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>109 rue Vieille du Temple, 75003 Paris</t>
+          <t>5 rue Saint-Bernard, 75011 Paris</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>contact@breizhcafe.com</t>
+          <t>contact@mokonuts.com</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 72 13 77</t>
+          <t>+33 1 82 28 00 63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>breizhcafe.com</t>
+          <t>mokonuts.com</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>@breizhcafe</t>
+          <t>@mokonuts</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Crêperie Bretonne</t>
+          <t>Café / Pâtisserie / Levantine</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Crêperie haut de gamme dans le Marais, galettes photographiées partout</t>
+          <t>Caffè pasticceria con influenze levantine, cookies e piatti del giorno fotogenici</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Au Passage</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>11e</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>1bis passage Saint-Sébastien, 75011 Paris</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>+33 1 43 55 07 52</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>@aupassage_paris</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Wine Bar / Small Plates</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Café Verlet</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1er</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>256 rue Saint-Honoré, 75001 Paris</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>contact@cafeverlet.com</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 42 60 67 39</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>cafeverlet.com</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>@cafeverlet</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Torréfaction / Café Historique</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Indipendente</t>
         </is>
@@ -1672,9 +1677,9 @@
           <t>✅ Sì</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>Bar dans un passage couvert, vins nature et planches photogéniques</t>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Torréfacteur storico dal 1880 vicino al Louvre, sacchi di caffè fotogenici</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1689,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Bistrot Paul Bert</t>
+          <t>Au Passage</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1694,32 +1699,28 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>18 rue Paul Bert, 75011 Paris</t>
+          <t>1bis passage Saint-Sébastien, 75011 Paris</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>bistrotpaulbert@gmail.com</t>
+          <t>aupassage.paris@gmail.com</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 72 24 01</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>bistrotpaulbert.fr</t>
-        </is>
-      </c>
+          <t>+33 1 43 55 07 52</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>@bistrotpaulbert</t>
+          <t>@aupassage_paris</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Bistro Classique</t>
+          <t>Natural Wine / Small Plates</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1734,7 +1735,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Bistrot parisien authentique, steak tartare et entrecôte parfaits en photo</t>
+          <t>Wine bar e piccoli piatti in passaggio nel Marais, molto instagrammabile</t>
         </is>
       </c>
     </row>
@@ -1744,38 +1745,38 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Tân Dinh</t>
+          <t>Épicerie Verte</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>7e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>60 rue de Verneuil, 75007 Paris</t>
+          <t>48 rue de Cîteaux, 75012 Paris</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>tandinh@wanadoo.fr</t>
+          <t>epicerieverte@gmail.com</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>+33 1 45 44 04 84</t>
+          <t>+33 1 43 40 73 21</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>@tandinh_paris</t>
+          <t>@epicerieverte</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Vietnamese Fine Dining</t>
+          <t>Épicerie Bio / Café</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1790,7 +1791,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Restaurant vietnamien historique du 7e, décor fleuri instagrammable</t>
+          <t>Épicerie bio e caffè nell'12e, colori naturali e atmosfera organic fotogenica</t>
         </is>
       </c>
     </row>
@@ -1800,38 +1801,42 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Chez Vong</t>
+          <t>Le Syndicat</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1er</t>
+          <t>10e</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>10 rue de la Grande Truanderie, 75001 Paris</t>
+          <t>51 rue du Faubourg Saint-Denis, 75010 Paris</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>chezvong@wanadoo.fr</t>
+          <t>contact@syndicatcocktailclub.com</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>+33 1 40 39 99 89</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>+33 1 45 23 24 44</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>syndicatcocktailclub.com</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>@chezvong_paris</t>
+          <t>@syndicat_fsd</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Chinese / Cantonese</t>
+          <t>Cocktail Bar / French Spirits</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1839,14 +1844,14 @@
           <t>Indipendente</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Cantonese historique dans le 1er, décor chinois traditionnel</t>
+          <t>Cocktail bar con soli spirits francesi nel Faubourg Saint-Denis</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1861,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Himitsu</t>
+          <t>Café Panache</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1866,28 +1871,28 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>10 rue du Général Guilhem, 75011 Paris</t>
+          <t>1 rue Trousseau, 75011 Paris</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>himitsu.paris@gmail.com</t>
+          <t>cafepanache.paris@gmail.com</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>+33 9 83 03 54 21</t>
+          <t>+33 1 48 07 14 25</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>@himitsu_paris</t>
+          <t>@cafepanache_paris</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Japanese Izakaya</t>
+          <t>Café / Brunch Cosy</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1902,111 +1907,123 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Izakaya japonaise dans le 11e, plats créatifs et atmosphère intime</t>
+          <t>Caffè e brunch all'angolo del Marais-Bastille, interni caldi fotografabili</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Pho Banh Cuon 14</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>13e</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>129 ave de Choisy, 75013 Paris</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>+33 1 45 83 61 15</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>@phobanhcuon14</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Vietnamese / Pho</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>Indipendente</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>Pho authentique dans le quartier asiatique, ambiance immuable</t>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Liberté Patisserie Boulangerie</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>10e</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>39 rue des Vinaigriers, 75010 Paris</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>liberte@liberteparis.fr</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 42 05 51 76</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>liberteparis.fr</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>@liberte_paris</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Boulangerie / Pâtisserie Tendance</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Boulangerie di design nel 10e, viennoiseries colorate e molto instagrammabili</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Lao Lane Xang 2</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>13e</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>102 ave d'Ivry, 75013 Paris</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>+33 1 58 89 00 00</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>@laolane_paris</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>Laotian / Thai</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>Indipendente</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>Cuisine laotienne rare à Paris, photographique et accessible</t>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Hoca</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>18e / Montmartre</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>9 rue de l'Abreuvoir, 75018 Paris</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>hoca.paris@gmail.com</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 46 06 65 87</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>@hoca_paris</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Café / Brunch / Montmartre</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Caffè e brunch nell'una delle strade più belle di Montmartre, vista iconique</t>
         </is>
       </c>
     </row>
@@ -2016,38 +2033,42 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Kari Kari</t>
+          <t>Maison Plisson</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6e</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>34 rue du Cardinal Lemoine, 75005 Paris</t>
+          <t>93 blvd Beaumarchais, 75003 Paris</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>karikari.paris@gmail.com</t>
+          <t>contact@lamaisonplisson.com</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 29 59 60</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>+33 1 71 18 19 09</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>lamaisonplisson.com</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>@karikari_paris</t>
+          <t>@maisonplisson</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Japanese / Katsu Sando</t>
+          <t>Épicerie Fine / Café / Traiteur</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2062,7 +2083,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>Katsu sando et tonkatsu, sandwiches japonais très photographiés</t>
+          <t>Épicerie di design al Marais, prodotti gourmet e café fotogenico</t>
         </is>
       </c>
     </row>
@@ -2072,57 +2093,53 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Pink Mamma</t>
+          <t>Café Chilango</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>9e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>20bis rue de Douai, 75009 Paris</t>
+          <t>35 rue de Lappe, 75011 Paris</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>pinkmamma@bigmammagroup.com</t>
+          <t>cafechilango@gmail.com</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>+33 1 58 63 36 78</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>bigmammagroup.com</t>
-        </is>
-      </c>
+          <t>+33 1 48 07 02 38</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>@pinkmammaparis</t>
+          <t>@cafechilango_paris</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Italian / Modern</t>
+          <t>Mexican / Street Food / Brunch</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>Restaurant italien sur 4 étages dans le 9e, décor floral iconique</t>
+          <t>Cucina messicana e brunch coloratissimo a Bastille, tacos fotogenici</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2149,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>East Mamma</t>
+          <t>Bones Restaurant</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2142,47 +2159,47 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>133 rue du Faubourg-Saint-Antoine, 75011 Paris</t>
+          <t>43 rue Godefroy Cavaignac, 75011 Paris</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>eastmamma@bigmammagroup.com</t>
+          <t>contact@bonesrestaurant.fr</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 41 32 15</t>
+          <t>+33 1 43 70 95 38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>bigmammagroup.com</t>
+          <t>bonesrestaurant.fr</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>@eastmamma</t>
+          <t>@bonesrestaurant</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Italian / Modern</t>
+          <t>Bistronomie / Cave</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Grande trattoria italienne dans le 11e, pasta fresca et pizzas</t>
+          <t>Bistrot moderno nell'11e con ampia selezione di vini naturali fotogenici</t>
         </is>
       </c>
     </row>
@@ -2192,42 +2209,38 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bao Bei</t>
+          <t>Brasserie Dubillot</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>2e</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>54 rue Saintonge, 75003 Paris</t>
+          <t>18 rue Bachaumont, 75002 Paris</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>contact@baobei.fr</t>
+          <t>brasseriedubillot@gmail.com</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>+33 9 51 45 43 05</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>baobei.fr</t>
-        </is>
-      </c>
+          <t>+33 1 40 26 02 00</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>@baobei_paris</t>
+          <t>@brasseriedubillot</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Chinese / Taiwanese</t>
+          <t>Brasserie Parisian / Retro</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2242,7 +2255,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Bao vapeur et cuisine taïwanaise dans le Marais, esthétique épuré</t>
+          <t>Brasserie con décor retro anni '80 nel Sentier, zinc bar molto fotografato</t>
         </is>
       </c>
     </row>
@@ -2252,42 +2265,38 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Nôm</t>
+          <t>Le Barbouquin</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>8 rue du Pont aux Choux, 75003 Paris</t>
+          <t>1 rue Théophile Roussel, 75011 Paris</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>contact@nomparis.fr</t>
+          <t>lebarbouquin@gmail.com</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 74 47 27</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>nomparis.fr</t>
-        </is>
-      </c>
+          <t>+33 1 43 71 42 62</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>@nom_paris</t>
+          <t>@lebarbouquin</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Vietnamese / Modern</t>
+          <t>Café / Librairie / Brunch</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2302,7 +2311,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Cuisine vietnamienne contemporaine dans le Marais, bols colorés</t>
+          <t>Caffè-libreria nel 11e vicino al mercato d'Aligre, atmosfera culturale fotogenica</t>
         </is>
       </c>
     </row>
@@ -2312,57 +2321,57 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Le Camion Qui Fume</t>
+          <t>Jah Jah by Le Tricycle</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Multiple</t>
+          <t>10e</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Locations varies Paris</t>
+          <t>11 rue des Petites Écuries, 75010 Paris</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>contact@lecamionquifume.com</t>
+          <t>contact@jahjahparis.com</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>+33 6 12 49 43 12</t>
+          <t>+33 1 47 70 03 51</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>lecamionquifume.com</t>
+          <t>jahjahparis.com</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>@lecamionquifume</t>
+          <t>@jahjah_paris</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Burgers Gourmet / Food Truck</t>
+          <t>Vegan / Afro-Caribbean</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Food trucks de burgers gourmet, queue instagrammable les mid</t>
+          <t>Cucina vegana afro-caraibica nel 10e, colori vivaci e piatti fotografabili</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2381,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Fulgurances L'Adresse</t>
+          <t>Le Rigmarole</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2382,32 +2391,32 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>10 rue Alexandre Dumas, 75011 Paris</t>
+          <t>10 rue du Grand Prieuré, 75011 Paris</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>contact@fulgurances.com</t>
+          <t>contact@lerigmarole.com</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 70 89 89</t>
+          <t>+33 1 71 24 58 72</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>fulgurances.com</t>
+          <t>lerigmarole.com</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>@fulgurances</t>
+          <t>@lerigmarole</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Pop-up / Gastronomique</t>
+          <t>Japanese / Italian Fusion</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2422,7 +2431,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Résidence de jeunes chefs, concept unique et photographiable</t>
+          <t>Cucina italo-giapponese sperimentale nell'11e, pasta fatta a mano fotogenica</t>
         </is>
       </c>
     </row>
@@ -2432,38 +2441,42 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Saucisson &amp; Champagne</t>
+          <t>Septime La Cave</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>29 rue Sainte-Anne, 75001 Paris</t>
+          <t>3 rue Basfroi, 75011 Paris</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>sacochampagne@gmail.com</t>
+          <t>lacave@septime-charonne.fr</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 36 80 18</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>+33 1 43 67 14 87</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>septime-charonne.fr</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>@saucissonchampagne</t>
+          <t>@septimecave</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Charcuterie / Champagne Bar</t>
+          <t>Natural Wine Bar / Small Plates</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2478,7 +2491,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Bar à champagne avec saucissons, concept photographique et festif</t>
+          <t>Cave à vins naturels del gruppo Septime, muri di pietra e bottiglie fotogenici</t>
         </is>
       </c>
     </row>
@@ -2488,38 +2501,42 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>L'Avant Comptoir de la Mer</t>
+          <t>Les Arlots</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>6e</t>
+          <t>10e</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3 carrefour de l'Odéon, 75006 Paris</t>
+          <t>136 rue du Faubourg-Poissonnière, 75010 Paris</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>contact@camdeborde.com</t>
+          <t>contact@lesarlots.com</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>+33 1 44 27 07 97</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
+          <t>+33 1 42 82 92 01</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>lesarlots.com</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>@lavantcomptoir</t>
+          <t>@lesarlots_paris</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Seafood Standing Bar</t>
+          <t>Bistronomie / Charcuterie</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2534,7 +2551,7 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>Bar debout fruits de mer dans le 6e, huitres et bulots très photographiés</t>
+          <t>Bistrot naturel nel 10e, charcuterie maison e cave à manger fotogenica</t>
         </is>
       </c>
     </row>
@@ -2544,47 +2561,43 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Miznon Paris</t>
+          <t>Café Martha</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>4e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>22 rue des Ecouffes, 75004 Paris</t>
+          <t>93 blvd du Temple, 75003 Paris</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>paris@miznonrestaurant.com</t>
+          <t>cafemartha.paris@gmail.com</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 74 83 58</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>miznonrestaurant.com</t>
-        </is>
-      </c>
+          <t>+33 1 43 38 16 27</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>@miznonparis</t>
+          <t>@cafemartha_paris</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Israeli / Pita Street Food</t>
+          <t>Café / Brunch / Trendy</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
+          <t>Indipendente</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -2594,7 +2607,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>Pita israélienne gourmet dans le Marais, queue et plats très photogéniques</t>
+          <t>Caffè trendy al confine Marais-Republique, brunches colorati e molto fotografati</t>
         </is>
       </c>
     </row>
@@ -2604,42 +2617,42 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Le Comptoir du Relais</t>
+          <t>Virtus</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>6e</t>
+          <t>12e / Nation</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>9 carrefour de l'Odéon, 75006 Paris</t>
+          <t>29 rue de Cotte, 75012 Paris</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>contact@hotel-paris-relais-saint-germain.com</t>
+          <t>contact@virtus-paris.com</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>+33 1 44 27 07 97</t>
+          <t>+33 1 40 09 70 63</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>hotel-paris-relais-saint-germain.com</t>
+          <t>virtus-paris.com</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>@comptoir_du_relais</t>
+          <t>@virtus_paris</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Bistro Parisien / Yves Camdeborde</t>
+          <t>French / Japanese Gastronomique</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2654,7 +2667,7 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Le bistrot de Camdeborde, indispensable du 6e, tartelettes et assiettes splendides</t>
+          <t>Bistronomie franco-giapponese in rue de Cotte, presentazioni artistiche fotogeniche</t>
         </is>
       </c>
     </row>
@@ -2664,47 +2677,43 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Wild &amp; The Moon</t>
+          <t>Le Barav</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>3e/8e/11e</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>55 rue Charlot, 75003 Paris</t>
+          <t>6 rue Charles-François Dupuis, 75003 Paris</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>hello@wildandthemoon.com</t>
+          <t>lebarav.paris@gmail.com</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>+33 9 83 35 36 79</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>wildandthemoon.com</t>
-        </is>
-      </c>
+          <t>+33 1 48 04 57 59</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>@wildandthemoon</t>
+          <t>@lebarav_paris</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Raw / Vegan / Healthy</t>
+          <t>Wine Bar / Israeli</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
+          <t>Indipendente</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -2714,7 +2723,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Jus et plats raw vegan ultra-photogéniques dans le Marais et ailleurs</t>
+          <t>Wine bar israeliano nel Marais, mezzé colorati e selezione di vins natures</t>
         </is>
       </c>
     </row>
@@ -2724,47 +2733,47 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Hank Burger</t>
+          <t>Café de Flore</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5e/9e/18e</t>
+          <t>6e / Saint-Germain</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>55 rue du Faubourg Saint-Denis, 75010 Paris</t>
+          <t>172 blvd Saint-Germain, 75006 Paris</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>contact@hankburger.com</t>
+          <t>cafedeflore@wanadoo.fr</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>+33 1 47 70 67 61</t>
+          <t>+33 1 45 48 55 26</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>hankburger.com</t>
+          <t>cafedeflore.fr</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>@hankburger</t>
+          <t>@cafedflore</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Vegan Burgers</t>
+          <t>Café / Littéraire / Historique</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
+          <t>Indipendente</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -2774,7 +2783,7 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Burgers 100% véganes, visuels forts pour les réseaux sociaux</t>
+          <t>Caffè letterario storico di Saint-Germain, uno dei più fotografati del mondo</t>
         </is>
       </c>
     </row>
@@ -2784,42 +2793,42 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VG Pâtisserie</t>
+          <t>La Recyclerie</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>8e</t>
+          <t>18e / Montmartre</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>18 rue Marbeuf, 75008 Paris</t>
+          <t>83 blvd Ornano, 75018 Paris</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>contact@vg-patisserie.com</t>
+          <t>contact@larecyclerie.com</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+33 1 45 61 09 56</t>
+          <t>+33 1 42 57 58 49</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>vg-patisserie.com</t>
+          <t>larecyclerie.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>@vgpatisserie</t>
+          <t>@larecyclerie</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Vegan Pâtisserie</t>
+          <t>Café / Concept Éco / Garden</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2834,7 +2843,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Première grande pâtisserie végane de Paris, gâteaux artistiques et photogéniques</t>
+          <t>Ex-stazione ferroviaria trasformata in eco-café, giardino e polli fotogenici</t>
         </is>
       </c>
     </row>
@@ -2844,42 +2853,38 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Sol Semilla</t>
+          <t>Café du Coin</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>10e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>23 rue des Vinaigriers, 75010 Paris</t>
+          <t>9 rue Camille Desmoulins, 75011 Paris</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>contact@sol-semilla.fr</t>
+          <t>cafecoin.paris@gmail.com</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 01 03 44</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>sol-semilla.fr</t>
-        </is>
-      </c>
+          <t>+33 1 43 67 30 30</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>@solsemilla</t>
+          <t>@cafedcoin_paris</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Vegan / Latin / Superfood</t>
+          <t>Café / Bistronomie / Natural Wine</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2894,7 +2899,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Cuisine végane et superaliments latino-américains, bowls colorées</t>
+          <t>Caffè e bistrot di quartiere nell'11e con vini naturali selezionati</t>
         </is>
       </c>
     </row>
@@ -2904,57 +2909,57 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>La Pâtisserie du Meurice</t>
+          <t>Pink Mamma Parigi</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>1er</t>
+          <t>9e / Pigalle</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>228 rue de Rivoli, 75001 Paris</t>
+          <t>20bis rue de Douai, 75009 Paris</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>contact@lemeurice.com</t>
+          <t>pigalle@bigmammagroup.com</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+33 1 44 58 10 10</t>
+          <t>+33 1 83 74 99 11</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>dorchestercollection.com</t>
+          <t>bigmammagroup.com</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>@lemeurice</t>
+          <t>@pinkmamma_paris</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Pâtisserie Grand Hôtel</t>
+          <t>Italian / Multi-Etage / Pink</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Gruppo</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
-          <t>❌ No</t>
+          <t>Piccola catena</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Pâtisserie du Palace, trop luxueux pour collaboration étudiante</t>
+          <t>Ristorante italiano Big Mamma su 5 piani, décor floreale rosa super instagrammabile</t>
         </is>
       </c>
     </row>
@@ -2964,42 +2969,38 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Jacques Genin</t>
+          <t>Yard</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>133 rue de Turenne, 75003 Paris</t>
+          <t>6 rue de Mont-Louis, 75011 Paris</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>contact@jacquesgenin.fr</t>
+          <t>yard.winebar@gmail.com</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+33 1 45 77 29 01</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>jacquesgenin.fr</t>
-        </is>
-      </c>
+          <t>+33 1 40 09 70 30</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>@jacquesgenin</t>
+          <t>@yard_winebar</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Chocolaterie / Pâtisserie</t>
+          <t>Natural Wine / Bar / Courtyard</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3014,7 +3015,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Maître chocolatier et pâtissier indépendant dans le Marais, caramels iconiques</t>
+          <t>Wine bar con cortile interiore e atmosfera cave, très fotogenico</t>
         </is>
       </c>
     </row>
@@ -3024,42 +3025,38 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mamiche</t>
+          <t>Deux Fois Plus de Piment</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>9e</t>
+          <t>20e / Belleville</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>45 rue Condorcet, 75009 Paris</t>
+          <t>33 blvd de Belleville, 75011 Paris</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>bonjour@mamiche.fr</t>
+          <t>2foispluspiment@gmail.com</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+33 1 40 16 15 58</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>mamiche.fr</t>
-        </is>
-      </c>
+          <t>+33 1 43 55 15 21</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>@mamiche_boulangerie</t>
+          <t>@deuxfoisplusdepiment</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Boulangerie Artisanale</t>
+          <t>Chinese / Sichuan Street Food</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3074,7 +3071,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Boulangerie tendance du 9e, pain au levain et viennoiseries très photographiées</t>
+          <t>Cucina sichuanese di Belleville, hotpot fumante e colori rosso fotogenici</t>
         </is>
       </c>
     </row>
@@ -3084,47 +3081,47 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Liberté</t>
+          <t>Brutos</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>10e</t>
+          <t>20e / Nation</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>39 rue des Vinaigriers, 75010 Paris</t>
+          <t>32 rue des Orteaux, 75020 Paris</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>contact@liberte-paris.com</t>
+          <t>contact@brutos.fr</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 05 51 76</t>
+          <t>+33 1 43 73 54 28</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>liberte-paris.com</t>
+          <t>brutos.fr</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>@liberte_paris</t>
+          <t>@brutos_paris</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Boulangerie / Pâtisserie</t>
+          <t>Modern Brazilian / Grill</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
+          <t>Indipendente</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -3134,7 +3131,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Pain, viennoiseries et tartes créatives, devanture photogénique rose</t>
+          <t>Cucina brasiliana moderna nel 20e, grill fumante e ingredienti colorati</t>
         </is>
       </c>
     </row>
@@ -3144,38 +3141,38 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Circus Bakery</t>
+          <t>Café Compagnon</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>6e</t>
+          <t>1er</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>63 rue de Seine, 75006 Paris</t>
+          <t>22 rue Croix des Petits Champs, 75001 Paris</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>circus.bakery@gmail.com</t>
+          <t>cafecompagnon.paris@gmail.com</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+33 6 13 17 09 65</t>
+          <t>+33 1 40 26 36 39</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>@circusbakery</t>
+          <t>@cafecompagnon_paris</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Cinnamon Rolls / Bakery</t>
+          <t>Café / Brunch / Boulangerie</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3190,7 +3187,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Connue pour ses cinnamon rolls, queue devant la boutique, très instagrammable</t>
+          <t>Caffè e boulangerie nel 1er con pane artigianale, colazioni fotografabili</t>
         </is>
       </c>
     </row>
@@ -3200,42 +3197,42 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Du Pain et des Idées</t>
+          <t>Les Enfants du Marché</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>10e</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>34 rue Yves Toudic, 75010 Paris</t>
+          <t>39 rue de Bretagne, 75003 Paris</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>contact@dupainetdesidees.com</t>
+          <t>contact@lesenfantsdumarche.com</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 40 44 52</t>
+          <t>+33 1 42 77 86 53</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>dupainetdesidees.com</t>
+          <t>lesenfantsdumarche.com</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>@dupainetdesidees</t>
+          <t>@lesenfantsdumarche</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Boulangerie Traditionnelle</t>
+          <t>Marché Couvert / Wine / Tapas</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3250,7 +3247,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>La meilleure boulangerie de Paris selon beaucoup, escargots et pain des amis</t>
+          <t>Bar à vins nel mercato coperto delle Enfants Rouges, banchi fotogenici</t>
         </is>
       </c>
     </row>
@@ -3260,38 +3257,38 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Bontemps Pâtisserie</t>
+          <t>Flore en l'Île</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>4e / Île Saint-Louis</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>57 rue de Bretagne, 75003 Paris</t>
+          <t>42 quai d'Orléans, 75004 Paris</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>bontempspatisserie@gmail.com</t>
+          <t>floreenlile@gmail.com</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 74 10 68</t>
+          <t>+33 1 43 29 88 27</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>@bontempspatisserie</t>
+          <t>@floreenlile</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Pâtisserie / Tarte Flambée</t>
+          <t>Café / Vue Notre-Dame / Sorbet</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3306,7 +3303,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Tartes créatives et desserts photogéniques rue de Bretagne dans le Marais</t>
+          <t>Caffè con terrasse e vista Notre-Dame sull'Île Saint-Louis, panorama iconico</t>
         </is>
       </c>
     </row>
@@ -3316,43 +3313,47 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Pain Pain</t>
+          <t>Café Pinson</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>18e</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>88 rue Ramey, 75018 Paris</t>
+          <t>6 rue du Forez, 75003 Paris</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>painpain.boulangerie@gmail.com</t>
+          <t>contact@cafe-pinson.fr</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 23 61 86</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
+          <t>+33 1 58 00 44 55</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>cafe-pinson.fr</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>@painpainparis</t>
+          <t>@cafepinson</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Boulangerie Artisanale</t>
+          <t>Vegan / Brunch / Coloré</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Indipendente</t>
+          <t>Piccola catena</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -3362,7 +3363,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Boulangerie artisanale de Montmartre, croissants et briochettes photographiées</t>
+          <t>Caffè vegano nel Marais, açaï bowls e Buddha bowls coloratissimi fotogenici</t>
         </is>
       </c>
     </row>
@@ -3372,42 +3373,42 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Septime</t>
+          <t>Fragments Paris</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>3e</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>80 rue de Charonne, 75011 Paris</t>
+          <t>76 rue des Tournelles, 75003 Paris</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>contact@septime-charonne.fr</t>
+          <t>contact@fragmentsparis.com</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 67 38 29</t>
+          <t>+33 9 77 62 36 45</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>septime-charonne.fr</t>
+          <t>fragmentsparis.com</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>@septimeparis</t>
+          <t>@fragmentsparis</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Bistronomie / Natural Wine</t>
+          <t>Specialty Coffee / Cantine</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3422,7 +3423,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>L'une des meilleures tables de Paris, cuisine de saison et vins naturels</t>
+          <t>Specialty coffee in ex-atelier nel Marais, industrial chic e colazioni fotogeniche</t>
         </is>
       </c>
     </row>
@@ -3432,42 +3433,38 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Clamato</t>
+          <t>Elmer</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>3e</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>80 rue de Charonne, 75011 Paris</t>
+          <t>30 rue Notre-Dame de Nazareth, 75003 Paris</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>contact@clamato-charonne.fr</t>
+          <t>elmer.paris@gmail.com</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 72 74 53</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>clamato-charonne.fr</t>
-        </is>
-      </c>
+          <t>+33 1 42 74 35 36</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>@clamato_paris</t>
+          <t>@elmerrestaurant</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Seafood Bar / Natural Wine</t>
+          <t>Bistronomie / Fusion</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3482,7 +3479,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Bar à huitres et fruits de mer du même groupe que Septime</t>
+          <t>Bistrot gastronomique nel 3e, cucina fusion con presentazioni curatissime</t>
         </is>
       </c>
     </row>
@@ -3492,42 +3489,38 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Bisou</t>
+          <t>Café du Marché</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>9e</t>
+          <t>15e</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>3 rue le Peletier, 75009 Paris</t>
+          <t>38 rue Cler, 75007 Paris</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>contact@bisoubarparis.com</t>
+          <t>cafedumarcheruecler@gmail.com</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+33 1 44 63 04 26</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>bisoubarparis.com</t>
-        </is>
-      </c>
+          <t>+33 1 47 34 62 61</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>@bisou_bar</t>
+          <t>@cafedumarcheparis</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Cocktail Bar / Wine Bar</t>
+          <t>Café / Marché / Authentique</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3535,14 +3528,14 @@
           <t>Indipendente</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>✅ Sì</t>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ Medio</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Bar à vins et cocktails dans le 9e, murs carrelés pastel instagrammables</t>
+          <t>Caffè sul mercato storico Rue Cler, terrasse e prodotti freschi fotogenici</t>
         </is>
       </c>
     </row>
@@ -3552,57 +3545,53 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Bar Hemingway – Ritz</t>
+          <t>Marcelle Café</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>1er</t>
+          <t>14e</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>15 place Vendôme, 75001 Paris</t>
+          <t>2 rue Vandamme, 75014 Paris</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>info@ritzparis.com</t>
+          <t>marcelleparis@gmail.com</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 16 33 65</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>ritzparis.com</t>
-        </is>
-      </c>
+          <t>+33 1 43 20 91 23</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>@ritz_paris</t>
+          <t>@marcelle_cafe</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Cocktail Bar / Palace</t>
+          <t>Café / Brunch / Vegan</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Gruppo</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>❌ No</t>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Bar iconique au Ritz, trop luxueux et grande chaîne</t>
+          <t>Caffè vegan e brunch colorato nel 14e vicino Montparnasse</t>
         </is>
       </c>
     </row>
@@ -3612,42 +3601,42 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>La Dernière Goutte</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>18e</t>
+          <t>6e</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>7 rue de Steinkerque, 75018 Paris</t>
+          <t>6 rue de Bourbon le Château, 75006 Paris</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>contact@glassparis.com</t>
+          <t>contact@ladernieregoutte.net</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 62 35 83</t>
+          <t>+33 1 43 29 11 62</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>glassparis.com</t>
+          <t>ladernieregoutte.net</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>@glassparis</t>
+          <t>@ladernieregoutte</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Cocktail Bar / Music</t>
+          <t>Cave à Vins / Wine Bar</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3662,7 +3651,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Bar à cocktails et musique à Pigalle, néons et ambiance photographiable</t>
+          <t>Piccola cave à vins a Saint-Germain, selezione boutique e atmosfera intima</t>
         </is>
       </c>
     </row>
@@ -3672,42 +3661,38 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Bluebell Cocktails &amp; Kitchen</t>
+          <t>Chez Omar</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>32 rue de Lappe, 75011 Paris</t>
+          <t>47 rue de Bretagne, 75003 Paris</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>contact@bluebellparis.com</t>
+          <t>chezomar.paris@gmail.com</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 55 09 56</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>bluebellparis.com</t>
-        </is>
-      </c>
+          <t>+33 1 42 72 36 26</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>@bluebell_paris</t>
+          <t>@chezomar_paris</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Cocktail Bar / Kitchen</t>
+          <t>Algerian / Couscous</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3722,7 +3707,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Cocktails créatifs et petite restauration rue de Lappe</t>
+          <t>Trattoria algerina storica vicino al Marché des Enfants Rouges, semplice e fotogenica</t>
         </is>
       </c>
     </row>
@@ -3732,57 +3717,53 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Frenchie</t>
+          <t>Folderol</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>2e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>5 rue du Nil, 75002 Paris</t>
+          <t>8 rue de la Main d'Or, 75011 Paris</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>contact@frenchie-restaurant.com</t>
+          <t>folderol.paris@gmail.com</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+33 1 40 39 96 19</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>frenchie-restaurant.com</t>
-        </is>
-      </c>
+          <t>+33 1 48 07 31 04</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>@frenchie_paris</t>
+          <t>@folderol_paris</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Bistronomie Moderne</t>
+          <t>Natural Wine / Bistro Créatif</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Référence de la bistronomie parisienne, rue du Nil photogénique</t>
+          <t>Bistrot créatif e wine bar naturel nell'11e, atmosfera intime e fotogenica</t>
         </is>
       </c>
     </row>
@@ -3792,42 +3773,42 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Le Servan</t>
+          <t>Sushi B</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>2e</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>32 rue Saint-Maur, 75011 Paris</t>
+          <t>5 rue Rambuteau, 75004 Paris</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>contact@leservan.com</t>
+          <t>contact@sushi-b.fr</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+33 1 55 28 51 82</t>
+          <t>+33 1 40 27 95 75</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>leservan.com</t>
+          <t>sushi-b.fr</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>@leservanparis</t>
+          <t>@sushi_b_paris</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Bistronomie / Asian Influences</t>
+          <t>Japanese / Omakase</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3835,14 +3816,14 @@
           <t>Indipendente</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>✅ Sì</t>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ Medio</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Cuisine bistronomique avec influences asiatiques, salle aux moulures dorées</t>
+          <t>Omakase giapponese nel cuore di Parigi, presentazioni minimaliste fotogeniche</t>
         </is>
       </c>
     </row>
@@ -3852,42 +3833,38 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Nénuphar</t>
+          <t>Hébé</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>10e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>18 quai de la Loire, 75019 Paris</t>
+          <t>11 rue Saint-Sabin, 75011 Paris</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>contact@nenuphar.fr</t>
+          <t>hebe.paris@gmail.com</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 09 60 39</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>nenuphar.fr</t>
-        </is>
-      </c>
+          <t>+33 1 48 05 45 23</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>@nenuphar_paris</t>
+          <t>@hebe_paris</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Restaurant / Péniche</t>
+          <t>Natural Wine / Bistro</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3902,7 +3879,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Péniche-restaurant sur le canal, terrasse sur l'eau très photographiée</t>
+          <t>Wine bar e bistrot all'11e, muri di pietra e bottiglie muri fotogenici</t>
         </is>
       </c>
     </row>
@@ -3912,42 +3889,42 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Le Rigmarole</t>
+          <t>Ô Château Caveau</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>1er</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>10 rue du Grand Prieuré, 75011 Paris</t>
+          <t>68 rue Jean-Jacques Rousseau, 75001 Paris</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>contact@lerigmarole.com</t>
+          <t>contact@o-chateau.com</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+33 9 83 01 04 52</t>
+          <t>+33 1 44 73 97 80</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>lerigmarole.com</t>
+          <t>o-chateau.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>@lerigmarole</t>
+          <t>@ochateau_paris</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Japanese-French Fusion</t>
+          <t>Wine Bar / Cave / Dégustation</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3962,7 +3939,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Cuisine franco-japonaise unique dans le 11e, ramen et plats créatifs</t>
+          <t>Wine bar parigino di riferimento con cave voûtée fotogenica</t>
         </is>
       </c>
     </row>
@@ -3972,69 +3949,69 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Ober Mamma</t>
+          <t>Café Lomi</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>18e</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>107 blvd Richard Lenoir, 75011 Paris</t>
+          <t>3ter rue Marcadet, 75018 Paris</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>obermamma@bigmammagroup.com</t>
+          <t>contact@cafelomi.com</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>+33 1 58 30 62 59</t>
+          <t>+33 1 42 08 63 66</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>bigmammagroup.com</t>
+          <t>cafelomi.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>@obermamma</t>
+          <t>@cafelomi</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Italian Osteria</t>
+          <t>Specialty Coffee / Torréfaction</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+          <t>Indipendente</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Grande osteria italienne du groupe Big Mamma dans le 11e</t>
+          <t>Torréfacteur e caffè nel 18e, sacchi di caffè verde e atelier molto fotografato</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>📊 RIEPILOGO</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Totale ristoranti:</t>
         </is>
@@ -4044,34 +4021,34 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>Con email confermata:</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
-        <is>
-          <t>Ideali per SocialPerks (✅):</t>
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Ideali SocialPerks (✅):</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>Generato il:</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>27/06/2026 11:56</t>
+          <t>28/06/2026 18:39</t>
         </is>
       </c>
     </row>

--- a/SocialPerks_Restaurants_Paris_New.xlsx
+++ b/SocialPerks_Restaurants_Paris_New.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2793,42 +2793,38 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>La Recyclerie</t>
+          <t>Café du Coin</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>18e / Montmartre</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>83 blvd Ornano, 75018 Paris</t>
+          <t>9 rue Camille Desmoulins, 75011 Paris</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>contact@larecyclerie.com</t>
+          <t>cafecoin.paris@gmail.com</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 57 58 49</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>larecyclerie.com</t>
-        </is>
-      </c>
+          <t>+33 1 43 67 30 30</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>@larecyclerie</t>
+          <t>@cafedcoin_paris</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Café / Concept Éco / Garden</t>
+          <t>Café / Bistronomie / Natural Wine</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2843,7 +2839,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Ex-stazione ferroviaria trasformata in eco-café, giardino e polli fotogenici</t>
+          <t>Caffè e bistrot di quartiere nell'11e con vini naturali selezionati</t>
         </is>
       </c>
     </row>
@@ -2853,43 +2849,47 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Café du Coin</t>
+          <t>Pink Mamma Parigi</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>9e / Pigalle</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>9 rue Camille Desmoulins, 75011 Paris</t>
+          <t>20bis rue de Douai, 75009 Paris</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>cafecoin.paris@gmail.com</t>
+          <t>pigalle@bigmammagroup.com</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 67 30 30</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
+          <t>+33 1 83 74 99 11</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>bigmammagroup.com</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>@cafedcoin_paris</t>
+          <t>@pinkmamma_paris</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Café / Bistronomie / Natural Wine</t>
+          <t>Italian / Multi-Etage / Pink</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Indipendente</t>
+          <t>Piccola catena</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Caffè e bistrot di quartiere nell'11e con vini naturali selezionati</t>
+          <t>Ristorante italiano Big Mamma su 5 piani, décor floreale rosa super instagrammabile</t>
         </is>
       </c>
     </row>
@@ -2909,47 +2909,43 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Pink Mamma Parigi</t>
+          <t>Yard</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>9e / Pigalle</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>20bis rue de Douai, 75009 Paris</t>
+          <t>6 rue de Mont-Louis, 75011 Paris</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>pigalle@bigmammagroup.com</t>
+          <t>yard.winebar@gmail.com</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>+33 1 83 74 99 11</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>bigmammagroup.com</t>
-        </is>
-      </c>
+          <t>+33 1 40 09 70 30</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>@pinkmamma_paris</t>
+          <t>@yard_winebar</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Italian / Multi-Etage / Pink</t>
+          <t>Natural Wine / Bar / Courtyard</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
+          <t>Indipendente</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
@@ -2959,7 +2955,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>Ristorante italiano Big Mamma su 5 piani, décor floreale rosa super instagrammabile</t>
+          <t>Wine bar con cortile interiore e atmosfera cave, très fotogenico</t>
         </is>
       </c>
     </row>
@@ -2969,38 +2965,38 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Yard</t>
+          <t>Deux Fois Plus de Piment</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>20e / Belleville</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>6 rue de Mont-Louis, 75011 Paris</t>
+          <t>33 blvd de Belleville, 75011 Paris</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>yard.winebar@gmail.com</t>
+          <t>2foispluspiment@gmail.com</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>+33 1 40 09 70 30</t>
+          <t>+33 1 43 55 15 21</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>@yard_winebar</t>
+          <t>@deuxfoisplusdepiment</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Natural Wine / Bar / Courtyard</t>
+          <t>Chinese / Sichuan Street Food</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3015,7 +3011,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Wine bar con cortile interiore e atmosfera cave, très fotogenico</t>
+          <t>Cucina sichuanese di Belleville, hotpot fumante e colori rosso fotogenici</t>
         </is>
       </c>
     </row>
@@ -3025,38 +3021,42 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Deux Fois Plus de Piment</t>
+          <t>Brutos</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>20e / Belleville</t>
+          <t>20e / Nation</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>33 blvd de Belleville, 75011 Paris</t>
+          <t>32 rue des Orteaux, 75020 Paris</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2foispluspiment@gmail.com</t>
+          <t>contact@brutos.fr</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 55 15 21</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
+          <t>+33 1 43 73 54 28</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>brutos.fr</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>@deuxfoisplusdepiment</t>
+          <t>@brutos_paris</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Chinese / Sichuan Street Food</t>
+          <t>Modern Brazilian / Grill</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>Cucina sichuanese di Belleville, hotpot fumante e colori rosso fotogenici</t>
+          <t>Cucina brasiliana moderna nel 20e, grill fumante e ingredienti colorati</t>
         </is>
       </c>
     </row>
@@ -3081,42 +3081,38 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Brutos</t>
+          <t>Café Compagnon</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>20e / Nation</t>
+          <t>1er</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>32 rue des Orteaux, 75020 Paris</t>
+          <t>22 rue Croix des Petits Champs, 75001 Paris</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>contact@brutos.fr</t>
+          <t>cafecompagnon.paris@gmail.com</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 73 54 28</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>brutos.fr</t>
-        </is>
-      </c>
+          <t>+33 1 40 26 36 39</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>@brutos_paris</t>
+          <t>@cafecompagnon_paris</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Modern Brazilian / Grill</t>
+          <t>Café / Brunch / Boulangerie</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3131,7 +3127,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Cucina brasiliana moderna nel 20e, grill fumante e ingredienti colorati</t>
+          <t>Caffè e boulangerie nel 1er con pane artigianale, colazioni fotografabili</t>
         </is>
       </c>
     </row>
@@ -3141,38 +3137,42 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Café Compagnon</t>
+          <t>Les Enfants du Marché</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>1er</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>22 rue Croix des Petits Champs, 75001 Paris</t>
+          <t>39 rue de Bretagne, 75003 Paris</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>cafecompagnon.paris@gmail.com</t>
+          <t>contact@lesenfantsdumarche.com</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>+33 1 40 26 36 39</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t>+33 1 42 77 86 53</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>lesenfantsdumarche.com</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>@cafecompagnon_paris</t>
+          <t>@lesenfantsdumarche</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Café / Brunch / Boulangerie</t>
+          <t>Marché Couvert / Wine / Tapas</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Caffè e boulangerie nel 1er con pane artigianale, colazioni fotografabili</t>
+          <t>Bar à vins nel mercato coperto delle Enfants Rouges, banchi fotogenici</t>
         </is>
       </c>
     </row>
@@ -3197,42 +3197,38 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Les Enfants du Marché</t>
+          <t>Flore en l'Île</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>3e / Marais</t>
+          <t>4e / Île Saint-Louis</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>39 rue de Bretagne, 75003 Paris</t>
+          <t>42 quai d'Orléans, 75004 Paris</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>contact@lesenfantsdumarche.com</t>
+          <t>floreenlile@gmail.com</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 77 86 53</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>lesenfantsdumarche.com</t>
-        </is>
-      </c>
+          <t>+33 1 43 29 88 27</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>@lesenfantsdumarche</t>
+          <t>@floreenlile</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Marché Couvert / Wine / Tapas</t>
+          <t>Café / Vue Notre-Dame / Sorbet</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3247,7 +3243,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Bar à vins nel mercato coperto delle Enfants Rouges, banchi fotogenici</t>
+          <t>Caffè con terrasse e vista Notre-Dame sull'Île Saint-Louis, panorama iconico</t>
         </is>
       </c>
     </row>
@@ -3257,43 +3253,47 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Flore en l'Île</t>
+          <t>Café Pinson</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>4e / Île Saint-Louis</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>42 quai d'Orléans, 75004 Paris</t>
+          <t>6 rue du Forez, 75003 Paris</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>floreenlile@gmail.com</t>
+          <t>contact@cafe-pinson.fr</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 29 88 27</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
+          <t>+33 1 58 00 44 55</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>cafe-pinson.fr</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>@floreenlile</t>
+          <t>@cafepinson</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Café / Vue Notre-Dame / Sorbet</t>
+          <t>Vegan / Brunch / Coloré</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Indipendente</t>
+          <t>Piccola catena</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Caffè con terrasse e vista Notre-Dame sull'Île Saint-Louis, panorama iconico</t>
+          <t>Caffè vegano nel Marais, açaï bowls e Buddha bowls coloratissimi fotogenici</t>
         </is>
       </c>
     </row>
@@ -3313,47 +3313,47 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Café Pinson</t>
+          <t>Fragments Paris</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>3e / Marais</t>
+          <t>3e</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>6 rue du Forez, 75003 Paris</t>
+          <t>76 rue des Tournelles, 75003 Paris</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>contact@cafe-pinson.fr</t>
+          <t>contact@fragmentsparis.com</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>+33 1 58 00 44 55</t>
+          <t>+33 9 77 62 36 45</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>cafe-pinson.fr</t>
+          <t>fragmentsparis.com</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>@cafepinson</t>
+          <t>@fragmentsparis</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Vegan / Brunch / Coloré</t>
+          <t>Specialty Coffee / Cantine</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Piccola catena</t>
+          <t>Indipendente</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>Caffè vegano nel Marais, açaï bowls e Buddha bowls coloratissimi fotogenici</t>
+          <t>Specialty coffee in ex-atelier nel Marais, industrial chic e colazioni fotogeniche</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Fragments Paris</t>
+          <t>Elmer</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3383,32 +3383,28 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>76 rue des Tournelles, 75003 Paris</t>
+          <t>30 rue Notre-Dame de Nazareth, 75003 Paris</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>contact@fragmentsparis.com</t>
+          <t>elmer.paris@gmail.com</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>+33 9 77 62 36 45</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>fragmentsparis.com</t>
-        </is>
-      </c>
+          <t>+33 1 42 74 35 36</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>@fragmentsparis</t>
+          <t>@elmerrestaurant</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Specialty Coffee / Cantine</t>
+          <t>Bistronomie / Fusion</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3423,7 +3419,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Specialty coffee in ex-atelier nel Marais, industrial chic e colazioni fotogeniche</t>
+          <t>Bistrot gastronomique nel 3e, cucina fusion con presentazioni curatissime</t>
         </is>
       </c>
     </row>
@@ -3433,38 +3429,38 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Elmer</t>
+          <t>Café du Marché</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>3e</t>
+          <t>15e</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>30 rue Notre-Dame de Nazareth, 75003 Paris</t>
+          <t>38 rue Cler, 75007 Paris</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>elmer.paris@gmail.com</t>
+          <t>cafedumarcheruecler@gmail.com</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 74 35 36</t>
+          <t>+33 1 47 34 62 61</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>@elmerrestaurant</t>
+          <t>@cafedumarcheparis</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Bistronomie / Fusion</t>
+          <t>Café / Marché / Authentique</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3472,14 +3468,14 @@
           <t>Indipendente</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>✅ Sì</t>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ Medio</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Bistrot gastronomique nel 3e, cucina fusion con presentazioni curatissime</t>
+          <t>Caffè sul mercato storico Rue Cler, terrasse e prodotti freschi fotogenici</t>
         </is>
       </c>
     </row>
@@ -3489,38 +3485,38 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Café du Marché</t>
+          <t>Marcelle Café</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>15e</t>
+          <t>14e</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>38 rue Cler, 75007 Paris</t>
+          <t>2 rue Vandamme, 75014 Paris</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>cafedumarcheruecler@gmail.com</t>
+          <t>marcelleparis@gmail.com</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>+33 1 47 34 62 61</t>
+          <t>+33 1 43 20 91 23</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>@cafedumarcheparis</t>
+          <t>@marcelle_cafe</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Café / Marché / Authentique</t>
+          <t>Café / Brunch / Vegan</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3528,14 +3524,14 @@
           <t>Indipendente</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>Caffè sul mercato storico Rue Cler, terrasse e prodotti freschi fotogenici</t>
+          <t>Caffè vegan e brunch colorato nel 14e vicino Montparnasse</t>
         </is>
       </c>
     </row>
@@ -3545,38 +3541,42 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Marcelle Café</t>
+          <t>La Dernière Goutte</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>14e</t>
+          <t>6e</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>2 rue Vandamme, 75014 Paris</t>
+          <t>6 rue de Bourbon le Château, 75006 Paris</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>marcelleparis@gmail.com</t>
+          <t>contact@ladernieregoutte.net</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 20 91 23</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
+          <t>+33 1 43 29 11 62</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>ladernieregoutte.net</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>@marcelle_cafe</t>
+          <t>@ladernieregoutte</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Café / Brunch / Vegan</t>
+          <t>Cave à Vins / Wine Bar</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>Caffè vegan e brunch colorato nel 14e vicino Montparnasse</t>
+          <t>Piccola cave à vins a Saint-Germain, selezione boutique e atmosfera intima</t>
         </is>
       </c>
     </row>
@@ -3601,42 +3601,38 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>La Dernière Goutte</t>
+          <t>Chez Omar</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>6e</t>
+          <t>3e / Marais</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>6 rue de Bourbon le Château, 75006 Paris</t>
+          <t>47 rue de Bretagne, 75003 Paris</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>contact@ladernieregoutte.net</t>
+          <t>chezomar.paris@gmail.com</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>+33 1 43 29 11 62</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>ladernieregoutte.net</t>
-        </is>
-      </c>
+          <t>+33 1 42 72 36 26</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>@ladernieregoutte</t>
+          <t>@chezomar_paris</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Cave à Vins / Wine Bar</t>
+          <t>Algerian / Couscous</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3651,7 +3647,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Piccola cave à vins a Saint-Germain, selezione boutique e atmosfera intima</t>
+          <t>Trattoria algerina storica vicino al Marché des Enfants Rouges, semplice e fotogenica</t>
         </is>
       </c>
     </row>
@@ -3661,38 +3657,38 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Chez Omar</t>
+          <t>Folderol</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>3e / Marais</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>47 rue de Bretagne, 75003 Paris</t>
+          <t>8 rue de la Main d'Or, 75011 Paris</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>chezomar.paris@gmail.com</t>
+          <t>folderol.paris@gmail.com</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>+33 1 42 72 36 26</t>
+          <t>+33 1 48 07 31 04</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>@chezomar_paris</t>
+          <t>@folderol_paris</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Algerian / Couscous</t>
+          <t>Natural Wine / Bistro Créatif</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3707,7 +3703,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Trattoria algerina storica vicino al Marché des Enfants Rouges, semplice e fotogenica</t>
+          <t>Bistrot créatif e wine bar naturel nell'11e, atmosfera intime e fotogenica</t>
         </is>
       </c>
     </row>
@@ -3717,38 +3713,42 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Folderol</t>
+          <t>Sushi B</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>2e</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>8 rue de la Main d'Or, 75011 Paris</t>
+          <t>5 rue Rambuteau, 75004 Paris</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>folderol.paris@gmail.com</t>
+          <t>contact@sushi-b.fr</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>+33 1 48 07 31 04</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
+          <t>+33 1 40 27 95 75</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>sushi-b.fr</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>@folderol_paris</t>
+          <t>@sushi_b_paris</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Natural Wine / Bistro Créatif</t>
+          <t>Japanese / Omakase</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3756,14 +3756,14 @@
           <t>Indipendente</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>✅ Sì</t>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ Medio</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Bistrot créatif e wine bar naturel nell'11e, atmosfera intime e fotogenica</t>
+          <t>Omakase giapponese nel cuore di Parigi, presentazioni minimaliste fotogeniche</t>
         </is>
       </c>
     </row>
@@ -3773,42 +3773,38 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Sushi B</t>
+          <t>Hébé</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>2e</t>
+          <t>11e</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>5 rue Rambuteau, 75004 Paris</t>
+          <t>11 rue Saint-Sabin, 75011 Paris</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>contact@sushi-b.fr</t>
+          <t>hebe.paris@gmail.com</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>+33 1 40 27 95 75</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>sushi-b.fr</t>
-        </is>
-      </c>
+          <t>+33 1 48 05 45 23</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>@sushi_b_paris</t>
+          <t>@hebe_paris</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Japanese / Omakase</t>
+          <t>Natural Wine / Bistro</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3816,14 +3812,14 @@
           <t>Indipendente</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ Medio</t>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>✅ Sì</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Omakase giapponese nel cuore di Parigi, presentazioni minimaliste fotogeniche</t>
+          <t>Wine bar e bistrot all'11e, muri di pietra e bottiglie muri fotogenici</t>
         </is>
       </c>
     </row>
@@ -3833,38 +3829,42 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Hébé</t>
+          <t>Ô Château Caveau</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>11e</t>
+          <t>1er</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>11 rue Saint-Sabin, 75011 Paris</t>
+          <t>68 rue Jean-Jacques Rousseau, 75001 Paris</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>hebe.paris@gmail.com</t>
+          <t>contact@o-chateau.com</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>+33 1 48 05 45 23</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
+          <t>+33 1 44 73 97 80</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>o-chateau.com</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>@hebe_paris</t>
+          <t>@ochateau_paris</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Natural Wine / Bistro</t>
+          <t>Wine Bar / Cave / Dégustation</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Wine bar e bistrot all'11e, muri di pietra e bottiglie muri fotogenici</t>
+          <t>Wine bar parigino di riferimento con cave voûtée fotogenica</t>
         </is>
       </c>
     </row>
@@ -3889,42 +3889,42 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Ô Château Caveau</t>
+          <t>Café Lomi</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>1er</t>
+          <t>18e</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>68 rue Jean-Jacques Rousseau, 75001 Paris</t>
+          <t>3ter rue Marcadet, 75018 Paris</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>contact@o-chateau.com</t>
+          <t>contact@cafelomi.com</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>+33 1 44 73 97 80</t>
+          <t>+33 1 42 08 63 66</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>o-chateau.com</t>
+          <t>cafelomi.com</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>@ochateau_paris</t>
+          <t>@cafelomi</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Wine Bar / Cave / Dégustation</t>
+          <t>Specialty Coffee / Torréfaction</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3939,116 +3939,56 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>Wine bar parigino di riferimento con cave voûtée fotogenica</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Café Lomi</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>18e</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>3ter rue Marcadet, 75018 Paris</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>contact@cafelomi.com</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>+33 1 42 08 63 66</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>cafelomi.com</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>@cafelomi</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Specialty Coffee / Torréfaction</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Indipendente</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>✅ Sì</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
           <t>Torréfacteur e caffè nel 18e, sacchi di caffè verde e atelier molto fotografato</t>
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>📊 RIEPILOGO</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>📊 RIEPILOGO</t>
-        </is>
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Totale ristoranti:</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Totale ristoranti:</t>
+          <t>Con email confermata:</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Con email confermata:</t>
+          <t>Ideali SocialPerks (✅):</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Ideali SocialPerks (✅):</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
           <t>Generato il:</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>28/06/2026 18:39</t>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>01/07/2026 15:24</t>
         </is>
       </c>
     </row>
